--- a/SimpleDamageTracker/package/LangMod/JP/SourceSheet.xlsx
+++ b/SimpleDamageTracker/package/LangMod/JP/SourceSheet.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="70">
   <si>
     <t>id</t>
   </si>
@@ -60,19 +60,19 @@
     <t>mc_sdt_configDamage</t>
   </si>
   <si>
-    <t>ダメージ</t>
-  </si>
-  <si>
-    <t>Damage</t>
+    <t>与ダメージ</t>
+  </si>
+  <si>
+    <t>Damage Dealt</t>
   </si>
   <si>
     <t>mc_sdt_configDamageShare</t>
   </si>
   <si>
-    <t>ダメージ比率</t>
-  </si>
-  <si>
-    <t>Damage Share</t>
+    <t>与ダメージ比率</t>
+  </si>
+  <si>
+    <t>Damage Dealt Share</t>
   </si>
   <si>
     <t>mc_sdt_displayNoDamage</t>
@@ -208,6 +208,24 @@
   </si>
   <si>
     <t>Abbreviates damage values of 1 million or more using units such as M, B, and T.</t>
+  </si>
+  <si>
+    <t>mc_sdt_configDamageTaken</t>
+  </si>
+  <si>
+    <t>被ダメージ</t>
+  </si>
+  <si>
+    <t>Damage Taken</t>
+  </si>
+  <si>
+    <t>mc_sdt_configDamageTakenShare</t>
+  </si>
+  <si>
+    <t>被ダメージ比率</t>
+  </si>
+  <si>
+    <t>Damage Taken Share</t>
   </si>
 </sst>
 </file>
@@ -1098,8 +1116,28 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
     <row r="26" ht="15.75" customHeight="1"/>
     <row r="27" ht="15.75" customHeight="1"/>
     <row r="28" ht="15.75" customHeight="1"/>
